--- a/output/pdf_financials_xlsx/ENRT.xlsx
+++ b/output/pdf_financials_xlsx/ENRT.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.5119010000000001</v>
+        <v>1.224585</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.418925</v>
+        <v>0.665633</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.361225</v>
+        <v>0.513741</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.5119010000000001</v>
+        <v>-1.224585</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.418925</v>
+        <v>-0.665633</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.361225</v>
+        <v>-0.513741</v>
       </c>
     </row>
     <row r="12">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">

--- a/output/pdf_financials_xlsx/ENRT.xlsx
+++ b/output/pdf_financials_xlsx/ENRT.xlsx
@@ -2289,13 +2289,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.854599</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.586122</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.075947</v>
       </c>
     </row>
     <row r="116">
@@ -3867,7 +3867,11 @@
           <t>Net Income (Loss) $</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>-1.832178</v>
       </c>
@@ -4190,7 +4194,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>0.854599</v>
       </c>
@@ -4248,7 +4256,11 @@
           <t>Net proceeds from common shares issued for cash</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
